--- a/public/exports-from-60-with-coowners/65113015.xlsx
+++ b/public/exports-from-60-with-coowners/65113015.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863019</t>
+          <t xml:space="preserve">311863033</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">

--- a/public/exports-from-60-with-coowners/65113015.xlsx
+++ b/public/exports-from-60-with-coowners/65113015.xlsx
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863033</t>
+          <t xml:space="preserve">311863019</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873659</t>
+          <t xml:space="preserve">311873660</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artelia A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M129" t="inlineStr">

--- a/public/exports-from-60-with-coowners/65113015.xlsx
+++ b/public/exports-from-60-with-coowners/65113015.xlsx
@@ -9664,12 +9664,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873660</t>
+          <t xml:space="preserve">311873659</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
